--- a/data/trans_dic/IP31B_R_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31B_R_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,59; 33,44</t>
+          <t>22,74; 37,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,28; 43,33</t>
+          <t>18,83; 32,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,47; 36,43</t>
+          <t>23,0; 33,11</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,17; 39,0</t>
+          <t>17,56; 33,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,57; 33,74</t>
+          <t>23,17; 38,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,07; 33,98</t>
+          <t>22,05; 33,12</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,76; 44,59</t>
+          <t>21,84; 42,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,88; 47,46</t>
+          <t>20,26; 44,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,15; 41,52</t>
+          <t>22,81; 38,35</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,75; 63,84</t>
+          <t>34,26; 48,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,3; 49,32</t>
+          <t>30,99; 43,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,46; 56,19</t>
+          <t>34,19; 43,38</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,44; 36,17</t>
+          <t>23,72; 38,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24,35; 40,03</t>
+          <t>20,83; 34,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,54; 35,76</t>
+          <t>24,28; 34,28</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,62; 31,87</t>
+          <t>19,11; 38,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,34; 42,59</t>
+          <t>15,32; 32,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,03; 34,36</t>
+          <t>19,54; 31,82</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,39; 43,17</t>
+          <t>29,32; 36,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,58; 37,66</t>
+          <t>26,8; 32,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,39; 39,01</t>
+          <t>28,85; 33,63</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>35748</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44095</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69762</t>
+          <t>61041</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18753; 33736</t>
+          <t>27558; 45234</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34170; 58574</t>
+          <t>18757; 32866</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57764; 85997</t>
+          <t>50803; 73126</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>28600</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>28779</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52735</t>
+          <t>50922</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21636; 36425</t>
+          <t>15783; 29688</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17402; 31614</t>
+          <t>22109; 36482</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43173; 63568</t>
+          <t>40851; 61366</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>33564</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10399; 22334</t>
+          <t>12197; 23540</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15511; 29582</t>
+          <t>10535; 23258</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28270; 46681</t>
+          <t>24604; 41366</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>103</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>98934</t>
+          <t>79749</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88786</t>
+          <t>64365</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187720</t>
+          <t>144115</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76384; 136380</t>
+          <t>67080; 95242</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74517; 104122</t>
+          <t>54165; 75168</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>163359; 238682</t>
+          <t>126680; 160758</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33220</t>
+          <t>44277</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>50127</t>
+          <t>31757</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83347</t>
+          <t>76034</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25918; 41777</t>
+          <t>33979; 54468</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37935; 62372</t>
+          <t>24054; 39765</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69302; 97021</t>
+          <t>62820; 88702</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>15506</t>
+          <t>18817</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37428</t>
+          <t>34123</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10570; 21570</t>
+          <t>12587; 25533</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14729; 29400</t>
+          <t>10620; 22226</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28749; 46981</t>
+          <t>26410; 43023</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>284</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>217167</t>
+          <t>218279</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>250599</t>
+          <t>181519</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>467767</t>
+          <t>399798</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>188435; 276777</t>
+          <t>197006; 242694</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>222381; 273832</t>
+          <t>162577; 200136</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>429548; 533742</t>
+          <t>368784; 429984</t>
         </is>
       </c>
     </row>
